--- a/data/xlsx/asia-ttc--building-electrification.xlsx
+++ b/data/xlsx/asia-ttc--building-electrification.xlsx
@@ -646,7 +646,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -668,7 +670,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -690,7 +694,9 @@
       <c r="C18" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -712,7 +718,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -734,7 +742,9 @@
       <c r="C20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -756,7 +766,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -778,7 +790,9 @@
       <c r="C22" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -800,7 +814,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -822,7 +838,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -844,7 +862,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -866,7 +886,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -888,7 +910,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -910,7 +934,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -932,7 +958,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -954,7 +982,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -976,7 +1006,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>5</v>
       </c>
@@ -998,7 +1030,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -1020,7 +1054,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1042,7 +1078,9 @@
       <c r="C34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>6</v>
       </c>
@@ -1064,7 +1102,9 @@
       <c r="C35" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
